--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -1,112 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ModifierStackingGroup" sheetId="1" r:id="rId1"/>
+    <sheet name="ModifierStackingGroup" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="25">
-  <si>
-    <t>@table</t>
-  </si>
-  <si>
-    <t>ModifierStackingGroup</t>
-  </si>
-  <si>
-    <t>@mode</t>
-  </si>
-  <si>
-    <t>map</t>
-  </si>
-  <si>
-    <t>@key</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
-  </si>
-  <si>
-    <t>@schema</t>
-  </si>
-  <si>
-    <t>8ef4487cff48ffab</t>
-  </si>
-  <si>
-    <t>#name</t>
-  </si>
-  <si>
-    <t>stable_key</t>
-  </si>
-  <si>
-    <t>aggregation</t>
-  </si>
-  <si>
-    <t>comparator_expression_id</t>
-  </si>
-  <si>
-    <t>#field</t>
-  </si>
-  <si>
-    <t>#type</t>
-  </si>
-  <si>
-    <t>i32</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>enum&lt;ModifierAggregation&gt;</t>
-  </si>
-  <si>
-    <t>optional&lt;ref&lt;ValueExpression.id&gt;&gt;</t>
-  </si>
-  <si>
-    <t>#scope</t>
-  </si>
-  <si>
-    <t>#input</t>
-  </si>
-  <si>
-    <t>key;range=1..2147483647</t>
-  </si>
-  <si>
-    <t>length=1..160</t>
-  </si>
-  <si>
-    <t>#desc</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -125,13 +46,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -419,124 +407,226 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>24</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>@table</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ModifierStackingGroup</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>@mode</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>@key</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>@scope</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>@schema</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>8ef4487cff48ffab</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>#name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>comparator_expression_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>#field</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>stable_key</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>aggregation</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>comparator_expression_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>#type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>i32</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>enum&lt;ModifierAggregation&gt;</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>optional&lt;ref&lt;ValueExpression.id&gt;&gt;</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>#scope</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>#input</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>key;range=1..2147483647</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>length=1..160</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>#desc</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>24001</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>probe.asta.replace-by-caster</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ReplaceGroup</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>24980</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>v1b.trace-minor.additive</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,6 +629,21 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>36003</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>c01.trace-minor.additive</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,6 +644,21 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>46003</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>c02.trace-minor.additive</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,6 +659,21 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>56003</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>c03.trace-minor.additive</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,6 +674,21 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>66003</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>c04.trace-minor.additive</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -689,6 +689,21 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>76003</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>c05.trace-minor.additive</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,6 +704,21 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>86003</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>c06.trace-minor.additive</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -719,6 +719,21 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>96003</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>c07.trace-minor.additive</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,6 +734,21 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>106003</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>c08.trace-minor.additive</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -749,6 +749,21 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>116003</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>c09.trace-minor.additive</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -764,6 +764,21 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>126003</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>c10.trace-minor.additive</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -779,6 +779,21 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>136003</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>c11.trace-minor.additive</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,6 +794,21 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>216003</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>l01.light-cone-passive.additive</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -809,6 +809,21 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>226003</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>l02.light-cone-passive.additive</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -824,6 +824,21 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>236003</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>l03.light-cone-passive.additive</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -839,6 +839,21 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>246003</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>l04.light-cone-passive.additive</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -854,6 +854,21 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>256003</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>l05.light-cone-passive.additive</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -869,6 +869,21 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>266003</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>l06.light-cone-passive.additive</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,6 +884,21 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>276003</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>l07.light-cone-passive.additive</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,6 +899,21 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>286003</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>l08.light-cone-passive.additive</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,6 +914,21 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>296003</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>l09.light-cone-passive.additive</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -929,6 +929,21 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>306003</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>l10.light-cone-passive.additive</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -944,6 +944,21 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>316003</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>l11.light-cone-passive.additive</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -959,6 +959,24 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>970001</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>goal07.probe.modifier.strongest-comparator</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>StrongestByComparator</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>24801</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -977,6 +977,51 @@
         <v>24801</v>
       </c>
     </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>980522</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.hardy-leaf-defense</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>980525</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.engender-attack</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>980526</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.vigor-damage</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1022,6 +1022,36 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>990531</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.combat-speed-up</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>990532</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.targeting-speed-up</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1052,6 +1052,21 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1000531</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.obliteration</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1067,6 +1067,21 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1010531</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.molten-fusion</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1082,6 +1082,36 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1020531</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.chilling-light</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1020532</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.sword-formation</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1112,6 +1112,51 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1030531</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.charging</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1030532</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.intensifying-cold</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1030533</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.redeployment</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1157,6 +1157,36 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1040531</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.frigid-escalation</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1040532</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.def-down</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1187,6 +1187,36 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1060531</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.modifier-group.obituary-permanent</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1060532</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.modifier-group.obituary-burst</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,6 +1217,21 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1070531</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.modifier-group.griever</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1232,6 +1232,36 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1080531</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.modifier-group.def-down</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1080532</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.modifier-group.power-amplification</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -977,6 +977,291 @@
         <v>24801</v>
       </c>
     </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>980522</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.hardy-leaf-defense</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>980525</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.engender-attack</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>980526</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.vigor-damage</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>990531</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.combat-speed-up</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>990532</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s02.targeting-speed-up</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>1000531</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s03.obliteration</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>1010531</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.molten-fusion</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>1020531</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.chilling-light</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>1020532</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.sword-formation</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>1030531</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.charging</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>1030532</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.intensifying-cold</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>1030533</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.redeployment</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>1040531</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.frigid-escalation</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>1040532</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.def-down</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>1060531</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.modifier-group.obituary-permanent</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>1060532</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.modifier-group.obituary-burst</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>1070531</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.modifier-group.griever</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="n">
+        <v>1080531</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.modifier-group.def-down</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="n">
+        <v>1080532</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s11.modifier-group.power-amplification</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/config/data/ModifierStackingGroup.xlsx
+++ b/config/data/ModifierStackingGroup.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ModifierStackingGroup" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ModifierStackingGroup" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -24,16 +24,68 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF1F2937"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3A4A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9EEF5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3D6E8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDE5EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -41,12 +93,45 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -412,196 +497,210 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.7109375" customWidth="1" min="1" max="1"/>
+    <col width="12.7109375" customWidth="1" style="5" min="2" max="3"/>
+    <col width="25.7109375" customWidth="1" style="5" min="4" max="4"/>
+    <col width="32.7109375" customWidth="1" style="5" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>@table</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>ModifierStackingGroup</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>@mode</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>@key</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>@scope</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>@groups</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>@schema</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>8ef4487cff48ffab</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>11e31aae1f9d755f</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>#name</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>stable_key</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>aggregation</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>comparator_expression_id</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>#field</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>stable_key</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>aggregation</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>comparator_expression_id</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>#type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>i32</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>enum&lt;ModifierAggregation&gt;</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>optional&lt;ref&lt;ValueExpression.id&gt;&gt;</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>#scope</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>all</t>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>#groups</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>#input</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>key;range=1..2147483647</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>length=1..160</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>#desc</t>
         </is>
       </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n"/>
+      <c r="E7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" t="n">
-        <v>24001</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>24001</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -615,8 +714,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
-        <v>24980</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>24980</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -630,8 +731,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
-        <v>36003</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>36003</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -645,8 +748,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
-        <v>46003</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>46003</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -660,8 +765,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
-        <v>56003</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>56003</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -675,8 +782,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
-        <v>66003</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>66003</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -690,8 +799,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
-        <v>76003</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>76003</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -705,8 +816,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
-        <v>86003</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>86003</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -720,8 +833,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
-        <v>96003</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>96003</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -735,8 +850,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
-        <v>106003</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>106003</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -750,8 +867,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
-        <v>116003</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>116003</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -765,8 +884,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
-        <v>126003</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>126003</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -780,8 +901,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
-        <v>136003</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>136003</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -795,8 +918,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
-        <v>216003</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>216003</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -810,8 +935,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
-        <v>226003</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>226003</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -825,8 +952,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
-        <v>236003</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>236003</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -840,8 +969,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
-        <v>246003</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>246003</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -855,8 +986,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
-        <v>256003</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>256003</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -870,8 +1003,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="n">
-        <v>266003</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>266003</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -885,8 +1020,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="n">
-        <v>276003</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>276003</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -900,8 +1037,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="n">
-        <v>286003</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>286003</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -915,8 +1054,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="n">
-        <v>296003</v>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>296003</t>
+        </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -930,8 +1071,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="n">
-        <v>306003</v>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>306003</t>
+        </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -945,8 +1088,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="n">
-        <v>316003</v>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>316003</t>
+        </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -960,8 +1105,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="n">
-        <v>970001</v>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>970001</t>
+        </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -973,13 +1120,17 @@
           <t>StrongestByComparator</t>
         </is>
       </c>
-      <c r="E32" t="n">
-        <v>24801</v>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>24801</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="n">
-        <v>980522</v>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>980522</t>
+        </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -993,8 +1144,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="n">
-        <v>980525</v>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>980525</t>
+        </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1008,8 +1161,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="n">
-        <v>980526</v>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>980526</t>
+        </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1023,8 +1178,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="n">
-        <v>990531</v>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>990531</t>
+        </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1038,8 +1195,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="n">
-        <v>990532</v>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>990532</t>
+        </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1053,8 +1212,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="n">
-        <v>1000531</v>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>1000531</t>
+        </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1068,8 +1229,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="n">
-        <v>1010531</v>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1010531</t>
+        </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1083,12 +1246,14 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="n">
-        <v>1020531</v>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1040531</t>
+        </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>goal07.enemy.s05.chilling-light</t>
+          <t>goal07.enemy.s07.frigid-escalation</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1098,12 +1263,14 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="n">
-        <v>1020532</v>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1040532</t>
+        </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>goal07.enemy.s05.sword-formation</t>
+          <t>goal07.enemy.s07.def-down</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1113,12 +1280,14 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="n">
-        <v>1030531</v>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1060531</t>
+        </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>goal07.enemy.s06.charging</t>
+          <t>goal07.enemy.s09.modifier-group.obituary-permanent</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1128,12 +1297,14 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="n">
-        <v>1030532</v>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1060532</t>
+        </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>goal07.enemy.s06.intensifying-cold</t>
+          <t>goal07.enemy.s09.modifier-group.obituary-burst</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1143,12 +1314,14 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="n">
-        <v>1030533</v>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1070531</t>
+        </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>goal07.enemy.s06.redeployment</t>
+          <t>goal07.enemy.s10.modifier-group.griever</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1158,12 +1331,14 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="n">
-        <v>1040531</v>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1080531</t>
+        </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>goal07.enemy.s07.frigid-escalation</t>
+          <t>goal07.enemy.s11.modifier-group.def-down</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1173,12 +1348,14 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="n">
-        <v>1040532</v>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>1080532</t>
+        </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>goal07.enemy.s07.def-down</t>
+          <t>goal07.enemy.s11.modifier-group.power-amplification</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1189,11 +1366,11 @@
     </row>
     <row r="47">
       <c r="B47" t="n">
-        <v>1060531</v>
+        <v>146003</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.modifier-group.obituary-permanent</t>
+          <t>c12.trace-minor.additive</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1204,11 +1381,11 @@
     </row>
     <row r="48">
       <c r="B48" t="n">
-        <v>1060532</v>
+        <v>1020531</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.modifier-group.obituary-burst</t>
+          <t>goal07.enemy.s05.chilling-light</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1219,11 +1396,11 @@
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>1070531</v>
+        <v>1020532</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>goal07.enemy.s10.modifier-group.griever</t>
+          <t>goal07.enemy.s05.sword-formation</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1234,11 +1411,11 @@
     </row>
     <row r="50">
       <c r="B50" t="n">
-        <v>1080531</v>
+        <v>1030531</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>goal07.enemy.s11.modifier-group.def-down</t>
+          <t>goal07.enemy.s06.charging</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1249,11 +1426,11 @@
     </row>
     <row r="51">
       <c r="B51" t="n">
-        <v>1080532</v>
+        <v>1030532</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>goal07.enemy.s11.modifier-group.power-amplification</t>
+          <t>goal07.enemy.s06.intensifying-cold</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1262,7 +1439,31 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="B52" t="n">
+        <v>1030533</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.redeployment</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Sum</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B8:B1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Value outside range" error="Value must be an integer from 1 to 2147483647." promptTitle="Integer range" prompt="Enter an integer from 1 to 2147483647." type="whole">
+      <formula1>1</formula1>
+      <formula2>2147483647</formula2>
+    </dataValidation>
+    <dataValidation sqref="D8:D1007" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid enum value" error="Value must be one of: Sum, Product, Maximum, Minimum, Latest, Earliest, StrongestByComparator, UniquePerSource, ReplaceGroup" promptTitle="ModifierAggregation enum" prompt="Select a value from the dropdown." type="list">
+      <formula1>"Sum,Product,Maximum,Minimum,Latest,Earliest,StrongestByComparator,UniquePerSource,ReplaceGroup"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>